--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704593.1499931796</v>
+        <v>704593</v>
       </c>
       <c r="R2" t="n">
-        <v>6406100.040580379</v>
+        <v>6406100</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1989-07-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-07-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magdalena Agestam, Claes Tullbrink</t>
+          <t>Claes Tullbrink, Magdalena Agestam</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>96309</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704593.1499931796</v>
+        <v>704593</v>
       </c>
       <c r="R3" t="n">
-        <v>6406100.040580379</v>
+        <v>6406100</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>1989-07-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-07-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -906,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magdalena Agestam, Claes Tullbrink</t>
+          <t>Claes Tullbrink, Magdalena Agestam</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98581</v>
+        <v>98587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Claes Tullbrink, Magdalena Agestam</t>
+          <t>Magdalena Agestam, Claes Tullbrink</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98554</v>
+        <v>98560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Claes Tullbrink, Magdalena Agestam</t>
+          <t>Magdalena Agestam, Claes Tullbrink</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98587</v>
+        <v>98590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98560</v>
+        <v>98563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98566</v>
+        <v>98567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98567</v>
+        <v>98594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98594</v>
+        <v>98600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98627</v>
+        <v>98634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98600</v>
+        <v>98607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98634</v>
+        <v>98638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98607</v>
+        <v>98611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98638</v>
+        <v>98645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98611</v>
+        <v>98618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98648</v>
+        <v>98653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98621</v>
+        <v>98626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450289</v>
       </c>
       <c r="B2" t="n">
-        <v>98653</v>
+        <v>98661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>106450288</v>
       </c>
       <c r="B3" t="n">
-        <v>98626</v>
+        <v>98634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12914-2025 artfynd.xlsx
+++ b/artfynd/A 12914-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106450289</v>
+        <v>106450288</v>
       </c>
       <c r="B2" t="n">
-        <v>98661</v>
+        <v>99093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>219797</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106450288</v>
+        <v>106450289</v>
       </c>
       <c r="B3" t="n">
-        <v>98634</v>
+        <v>99120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219797</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
